--- a/reports/feb25 to jan26/Liability/Current Liabilities/Sundry Creditors/GrpSum.xlsx
+++ b/reports/feb25 to jan26/Liability/Current Liabilities/Sundry Creditors/GrpSum.xlsx
@@ -5,15 +5,30 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fc31808bb1f3f1ad/MANGEMENT FILE/Documents/Antigravity/Wilmer House/reports/feb25 to jan26/Liability/Current Liabilities/Sundry Creditors/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Antigravity\Wilmer House\reports\feb25 to jan26 - Copy\Liability\Current Liabilities\Sundry Creditors\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B198E5EC-BC0F-45A1-B73C-47E5F5585AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69A0F5C4-ADC7-4FB2-A66F-D597277A4F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="450" yWindow="20" windowWidth="18750" windowHeight="10180" xr2:uid="{799EB203-C377-4939-BC10-AC6259780C58}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="954" xr2:uid="{5A26D9F4-6F81-4501-AFBE-64F38B0AD2AB}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sundry Creditors_" sheetId="1" r:id="rId1"/>
+    <sheet name="Sundry Creditors" sheetId="1" r:id="rId1"/>
+    <sheet name="ARNWOOD TIMBER LIMITED Wilmer H" sheetId="2" r:id="rId2"/>
+    <sheet name="Carpet Barn &amp; Bedstore Wilmer H" sheetId="3" r:id="rId3"/>
+    <sheet name="Costco Wholesale Wilmer House" sheetId="4" r:id="rId4"/>
+    <sheet name="Iceland Wilmer House" sheetId="5" r:id="rId5"/>
+    <sheet name="Lidl Wilmer House" sheetId="6" r:id="rId6"/>
+    <sheet name="London Lintels Wilmer House" sheetId="7" r:id="rId7"/>
+    <sheet name="Metal Supermarkets Wilmer House" sheetId="8" r:id="rId8"/>
+    <sheet name="MKM Building Supplies Wilmer Ho" sheetId="9" r:id="rId9"/>
+    <sheet name="PLUMBFIX Wilmer House" sheetId="10" r:id="rId10"/>
+    <sheet name="Post Office Ltd wilmer house" sheetId="11" r:id="rId11"/>
+    <sheet name="Robert Dyas Wilmer House" sheetId="12" r:id="rId12"/>
+    <sheet name="Screwfix Direct Wilmer House" sheetId="13" r:id="rId13"/>
+    <sheet name="Toolstation Ltd Wilmer House" sheetId="14" r:id="rId14"/>
+    <sheet name="TRADEPOINT Wilmer House" sheetId="15" r:id="rId15"/>
+    <sheet name="Wickes Wilmer House" sheetId="16" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="136">
   <si>
     <t>WILMER HOUSE LTD</t>
   </si>
@@ -45,7 +60,7 @@
     <t>Group Summary</t>
   </si>
   <si>
-    <t>1-Jan-25 to 30-Jun-26</t>
+    <t>1-Feb-25 to 31-Jan-26</t>
   </si>
   <si>
     <t/>
@@ -118,6 +133,330 @@
   </si>
   <si>
     <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Ledger Account</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Vch Type</t>
+  </si>
+  <si>
+    <t>Vch No.</t>
+  </si>
+  <si>
+    <t>By</t>
+  </si>
+  <si>
+    <t>Shop Refurbishment</t>
+  </si>
+  <si>
+    <t>Purchase</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>To</t>
+  </si>
+  <si>
+    <t>Englabs Imprst</t>
+  </si>
+  <si>
+    <t>Journal</t>
+  </si>
+  <si>
+    <t>465</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>477</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>480</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>551</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>552</t>
+  </si>
+  <si>
+    <t>Costco Membership Item Ledger</t>
+  </si>
+  <si>
+    <t>449</t>
+  </si>
+  <si>
+    <t>Consumable Goods</t>
+  </si>
+  <si>
+    <t>451</t>
+  </si>
+  <si>
+    <t>Cash</t>
+  </si>
+  <si>
+    <t>555</t>
+  </si>
+  <si>
+    <t>Credit Card American Express</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>494</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>492</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>485</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>482</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>WILMER HOUSE LTD Bank</t>
+  </si>
+  <si>
+    <t>Payment</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Receipt</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>550</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>489</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>549</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>556</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>553</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>557</t>
+  </si>
+  <si>
+    <t>Delivery Expenses</t>
+  </si>
+  <si>
+    <t>454</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>456</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>458</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>USB Printing, Bulk Copies Item Ledger</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>476</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Salil Anand Imprest Account</t>
+  </si>
+  <si>
+    <t>471</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>474</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>475</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>478</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>479</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>558</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>498</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>499</t>
+  </si>
+  <si>
+    <t>501</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>559</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>505</t>
+  </si>
+  <si>
+    <t>561</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>562</t>
   </si>
 </sst>
 </file>
@@ -128,7 +467,7 @@
     <numFmt numFmtId="164" formatCode="&quot;&quot;0"/>
     <numFmt numFmtId="165" formatCode="&quot;&quot;0.00"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -173,6 +512,13 @@
       <b/>
       <i/>
       <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -264,12 +610,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -278,34 +621,13 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="4"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="4"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="4"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -333,6 +655,69 @@
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="8"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
@@ -648,7 +1033,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58FB8078-95B4-412B-B5BD-0C2672DDF7C2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{306DF392-5753-4C42-BCD6-7C793289B6F8}">
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -659,313 +1044,313 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="12" t="s">
+      <c r="D8" s="29"/>
+      <c r="E8" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="8" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="20">
+      <c r="B10" s="11"/>
+      <c r="C10" s="12">
         <v>750.14</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="12">
         <v>750.14</v>
       </c>
-      <c r="E10" s="19"/>
+      <c r="E10" s="11"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="20">
+      <c r="B11" s="11"/>
+      <c r="C11" s="12">
         <v>53</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="12">
         <v>53</v>
       </c>
-      <c r="E11" s="19"/>
+      <c r="E11" s="11"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="20">
+      <c r="B12" s="11"/>
+      <c r="C12" s="12">
         <v>145.15</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="12">
         <v>145.15</v>
       </c>
-      <c r="E12" s="19"/>
+      <c r="E12" s="11"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="20">
+      <c r="B13" s="11"/>
+      <c r="C13" s="12">
         <v>5.75</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="12">
         <v>5.75</v>
       </c>
-      <c r="E13" s="19"/>
+      <c r="E13" s="11"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="20">
+      <c r="B14" s="11"/>
+      <c r="C14" s="12">
         <v>33.950000000000003</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="12">
         <v>33.950000000000003</v>
       </c>
-      <c r="E14" s="19"/>
+      <c r="E14" s="11"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="20">
+      <c r="B15" s="11"/>
+      <c r="C15" s="12">
         <v>420.07</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="12">
         <v>420.07</v>
       </c>
-      <c r="E15" s="19"/>
+      <c r="E15" s="11"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="20">
+      <c r="B16" s="11"/>
+      <c r="C16" s="12">
         <v>306.04000000000002</v>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="12">
         <v>306.04000000000002</v>
       </c>
-      <c r="E16" s="19"/>
+      <c r="E16" s="11"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="20">
-        <v>927.84</v>
-      </c>
-      <c r="D17" s="20">
-        <v>927.84</v>
-      </c>
-      <c r="E17" s="19"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="12">
+        <v>869.92</v>
+      </c>
+      <c r="D17" s="12">
+        <v>869.92</v>
+      </c>
+      <c r="E17" s="11"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="20">
+      <c r="B18" s="11"/>
+      <c r="C18" s="12">
         <v>148.1</v>
       </c>
-      <c r="D18" s="20">
+      <c r="D18" s="12">
         <v>148.1</v>
       </c>
-      <c r="E18" s="19"/>
+      <c r="E18" s="11"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="19"/>
-      <c r="C19" s="20">
-        <v>36.6</v>
-      </c>
-      <c r="D19" s="20">
-        <v>36.6</v>
-      </c>
-      <c r="E19" s="19"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="12">
+        <v>31</v>
+      </c>
+      <c r="D19" s="12">
+        <v>31</v>
+      </c>
+      <c r="E19" s="11"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="20">
+      <c r="B20" s="11"/>
+      <c r="C20" s="12">
         <v>12</v>
       </c>
-      <c r="D20" s="20">
+      <c r="D20" s="12">
         <v>12</v>
       </c>
-      <c r="E20" s="19"/>
+      <c r="E20" s="11"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="20">
-        <v>34.99</v>
-      </c>
-      <c r="D21" s="20">
-        <v>34.99</v>
-      </c>
-      <c r="E21" s="19"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="12">
+        <v>20</v>
+      </c>
+      <c r="D21" s="12">
+        <v>20</v>
+      </c>
+      <c r="E21" s="11"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="19"/>
-      <c r="C22" s="20">
-        <v>491.35</v>
-      </c>
-      <c r="D22" s="20">
-        <v>491.35</v>
-      </c>
-      <c r="E22" s="19"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="12">
+        <v>447.29</v>
+      </c>
+      <c r="D22" s="12">
+        <v>447.29</v>
+      </c>
+      <c r="E22" s="11"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="19"/>
-      <c r="C23" s="20">
-        <v>62.6</v>
-      </c>
-      <c r="D23" s="20">
-        <v>62.6</v>
-      </c>
-      <c r="E23" s="19"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="12">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="D23" s="12">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="E23" s="11"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="20">
+      <c r="B24" s="11"/>
+      <c r="C24" s="12">
         <v>36.700000000000003</v>
       </c>
-      <c r="D24" s="20">
+      <c r="D24" s="12">
         <v>36.700000000000003</v>
       </c>
-      <c r="E24" s="19"/>
+      <c r="E24" s="11"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" s="21" t="s">
+      <c r="A25" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="22"/>
-      <c r="C25" s="23">
-        <v>3464.28</v>
-      </c>
-      <c r="D25" s="23">
-        <v>3464.28</v>
-      </c>
-      <c r="E25" s="22"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="15">
+        <v>3296.71</v>
+      </c>
+      <c r="D25" s="15">
+        <v>3296.71</v>
+      </c>
+      <c r="E25" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -981,4 +1366,3881 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47EFDEE6-7C42-44BA-B51C-30FEEBF6D669}">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="19">
+        <v>45861</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="F8" s="23"/>
+      <c r="G8" s="24">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="19">
+        <v>45861</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="F9" s="24">
+        <v>14.99</v>
+      </c>
+      <c r="G9" s="23"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="19">
+        <v>45870</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="F10" s="23"/>
+      <c r="G10" s="24">
+        <v>30.18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="19">
+        <v>45870</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="F11" s="24">
+        <v>30.18</v>
+      </c>
+      <c r="G11" s="23"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="19">
+        <v>45882</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="F12" s="23"/>
+      <c r="G12" s="24">
+        <v>102.93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="19">
+        <v>45882</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="F13" s="24">
+        <v>102.93</v>
+      </c>
+      <c r="G13" s="23"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="36">
+        <v>148.1</v>
+      </c>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="25">
+        <v>148.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE0606CE-F6C0-4A82-96B8-23C8AE78ACEC}">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="19">
+        <v>45847</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="F8" s="23"/>
+      <c r="G8" s="24">
+        <v>8.75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="19">
+        <v>45847</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="F9" s="24">
+        <v>8.75</v>
+      </c>
+      <c r="G9" s="23"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="19">
+        <v>45848</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="F10" s="23"/>
+      <c r="G10" s="24">
+        <v>8.75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="19">
+        <v>45848</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="F11" s="24">
+        <v>8.75</v>
+      </c>
+      <c r="G11" s="23"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="19">
+        <v>45849</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F12" s="23"/>
+      <c r="G12" s="24">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="19">
+        <v>45849</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="F13" s="24">
+        <v>13.5</v>
+      </c>
+      <c r="G13" s="23"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="36">
+        <v>31</v>
+      </c>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="25">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48A314F4-28E5-4C4D-AF0C-C5526AF88C35}">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="19">
+        <v>45868</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="F8" s="23"/>
+      <c r="G8" s="24">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="19">
+        <v>45868</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="F9" s="24">
+        <v>12</v>
+      </c>
+      <c r="G9" s="23"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="36">
+        <v>12</v>
+      </c>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="25">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEA17A4C-CFDD-4B64-9CCE-E03DB1BF8B96}">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="19">
+        <v>45865</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="F8" s="23"/>
+      <c r="G8" s="24">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="19">
+        <v>45865</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="F9" s="24">
+        <v>20</v>
+      </c>
+      <c r="G9" s="23"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="36">
+        <v>20</v>
+      </c>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="25">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C1A5774-0F7B-44FE-AE6E-032EC47D7D31}">
+  <dimension ref="A1:G43"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="19">
+        <v>45859</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="F8" s="23"/>
+      <c r="G8" s="24">
+        <v>9.7899999999999991</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="19">
+        <v>45859</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="F9" s="23"/>
+      <c r="G9" s="24">
+        <v>8.48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="19">
+        <v>45859</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="F10" s="24">
+        <v>8.48</v>
+      </c>
+      <c r="G10" s="23"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="19">
+        <v>45860</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="F11" s="23"/>
+      <c r="G11" s="24">
+        <v>12.98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="19">
+        <v>45860</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="F12" s="23"/>
+      <c r="G12" s="24">
+        <v>25.96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="19">
+        <v>45861</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="F13" s="23"/>
+      <c r="G13" s="24">
+        <v>53.98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="19">
+        <v>45861</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="F14" s="23"/>
+      <c r="G14" s="24">
+        <v>4.9800000000000004</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="19">
+        <v>45861</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="F15" s="23"/>
+      <c r="G15" s="24">
+        <v>63.63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="19">
+        <v>45861</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="F16" s="24">
+        <v>53.98</v>
+      </c>
+      <c r="G16" s="23"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="19">
+        <v>45862</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="F17" s="24">
+        <v>25.96</v>
+      </c>
+      <c r="G17" s="23"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="19">
+        <v>45863</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="F18" s="24">
+        <v>4.9800000000000004</v>
+      </c>
+      <c r="G18" s="23"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="19">
+        <v>45863</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="F19" s="24">
+        <v>63.63</v>
+      </c>
+      <c r="G19" s="23"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="19">
+        <v>45864</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="F20" s="23"/>
+      <c r="G20" s="24">
+        <v>16.37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="19">
+        <v>45864</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="F21" s="24">
+        <v>16.37</v>
+      </c>
+      <c r="G21" s="23"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="19">
+        <v>45865</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="F22" s="23"/>
+      <c r="G22" s="24">
+        <v>10.88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" s="19">
+        <v>45865</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="F23" s="24">
+        <v>10.88</v>
+      </c>
+      <c r="G23" s="23"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" s="19">
+        <v>45867</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="F24" s="23"/>
+      <c r="G24" s="24">
+        <v>26.22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" s="19">
+        <v>45867</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="F25" s="24">
+        <v>26.22</v>
+      </c>
+      <c r="G25" s="23"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" s="19">
+        <v>45867</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="F26" s="23"/>
+      <c r="G26" s="24">
+        <v>23.35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" s="19">
+        <v>45867</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="F27" s="24">
+        <v>23.35</v>
+      </c>
+      <c r="G27" s="23"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" s="19">
+        <v>45869</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="F28" s="23"/>
+      <c r="G28" s="24">
+        <v>5.89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" s="19">
+        <v>45869</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="F29" s="24">
+        <v>28.66</v>
+      </c>
+      <c r="G29" s="23"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30" s="19">
+        <v>45872</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="F30" s="23"/>
+      <c r="G30" s="24">
+        <v>21.02</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31" s="19">
+        <v>45872</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="F31" s="24">
+        <v>21.02</v>
+      </c>
+      <c r="G31" s="23"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32" s="19">
+        <v>45876</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E32" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="F32" s="23"/>
+      <c r="G32" s="24">
+        <v>16.84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33" s="19">
+        <v>45876</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="F33" s="24">
+        <v>16.84</v>
+      </c>
+      <c r="G33" s="23"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34" s="19">
+        <v>45877</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E34" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="F34" s="23"/>
+      <c r="G34" s="24">
+        <v>21.38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35" s="19">
+        <v>45877</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D35" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E35" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="F35" s="24">
+        <v>21.38</v>
+      </c>
+      <c r="G35" s="23"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" s="19">
+        <v>45879</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D36" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E36" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="F36" s="23"/>
+      <c r="G36" s="24">
+        <v>31.89</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" s="19">
+        <v>45879</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D37" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E37" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="F37" s="24">
+        <v>31.89</v>
+      </c>
+      <c r="G37" s="23"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38" s="19">
+        <v>45880</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D38" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E38" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="F38" s="23"/>
+      <c r="G38" s="24">
+        <v>89.96</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39" s="19">
+        <v>45880</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D39" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E39" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="F39" s="24">
+        <v>34.979999999999997</v>
+      </c>
+      <c r="G39" s="23"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40" s="19">
+        <v>45881</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D40" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E40" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="F40" s="23"/>
+      <c r="G40" s="24">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A41" s="19">
+        <v>45881</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D41" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E41" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="F41" s="24">
+        <v>3.69</v>
+      </c>
+      <c r="G41" s="23"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A42" s="19">
+        <v>45882</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D42" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E42" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="F42" s="24">
+        <v>54.98</v>
+      </c>
+      <c r="G42" s="23"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43" s="36">
+        <v>447.29</v>
+      </c>
+      <c r="B43" s="36"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="36"/>
+      <c r="E43" s="36"/>
+      <c r="F43" s="36"/>
+      <c r="G43" s="25">
+        <v>447.29</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EFE3507-BC2C-4176-AEBE-ABAB2F96C7C7}">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="19">
+        <v>45872</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="F8" s="23"/>
+      <c r="G8" s="24">
+        <v>17.600000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="19">
+        <v>45872</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="F9" s="24">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="G9" s="23"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="36">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="25">
+        <v>17.600000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0907080-79B1-4265-A292-802A59EF6918}">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="19">
+        <v>45881</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="23"/>
+      <c r="G8" s="24">
+        <v>36.700000000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="19">
+        <v>45881</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="F9" s="24">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="G9" s="23"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="36">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="25">
+        <v>36.700000000000003</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C8B063A-ACDD-4AC5-9D42-7E119C1E1BE1}">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="19">
+        <v>45860</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="23"/>
+      <c r="G8" s="24">
+        <v>308.72000000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="19">
+        <v>45860</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="24">
+        <v>308.72000000000003</v>
+      </c>
+      <c r="G9" s="23"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="19">
+        <v>45866</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="23"/>
+      <c r="G10" s="24">
+        <v>327.74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="19">
+        <v>45866</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="24">
+        <v>327.74</v>
+      </c>
+      <c r="G11" s="23"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="19">
+        <v>45868</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="23"/>
+      <c r="G12" s="24">
+        <v>113.68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="19">
+        <v>45868</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="24">
+        <v>113.68</v>
+      </c>
+      <c r="G13" s="23"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="36">
+        <v>750.14</v>
+      </c>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="25">
+        <v>750.14</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A2B03D7-D29B-476E-89C6-39FA181446F4}">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="19">
+        <v>45880</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="23"/>
+      <c r="G8" s="24">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="19">
+        <v>45880</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="24">
+        <v>27</v>
+      </c>
+      <c r="G9" s="23"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="19">
+        <v>45882</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="23"/>
+      <c r="G10" s="24">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="19">
+        <v>45882</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="24">
+        <v>26</v>
+      </c>
+      <c r="G11" s="23"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="36">
+        <v>53</v>
+      </c>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="25">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BF9D53C-CACF-47E6-BCCE-018F112583A9}">
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="19">
+        <v>45844</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="23"/>
+      <c r="G8" s="24">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="19">
+        <v>45844</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="23"/>
+      <c r="G9" s="24">
+        <v>67.150000000000006</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="19">
+        <v>45844</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="24">
+        <v>10</v>
+      </c>
+      <c r="G10" s="23"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="19">
+        <v>45844</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="24">
+        <v>57.15</v>
+      </c>
+      <c r="G11" s="23"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="19">
+        <v>45844</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="24">
+        <v>78</v>
+      </c>
+      <c r="G12" s="23"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="36">
+        <v>145.15</v>
+      </c>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="25">
+        <v>145.15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45ED5FBC-E19A-4CE1-A095-68434A91F107}">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="19">
+        <v>45875</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="23"/>
+      <c r="G8" s="24">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="19">
+        <v>45875</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="24">
+        <v>5.75</v>
+      </c>
+      <c r="G9" s="23"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="36">
+        <v>5.75</v>
+      </c>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="25">
+        <v>5.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EB2873A-972C-4166-BE5A-485AA8EF5F76}">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="19">
+        <v>45872</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="23"/>
+      <c r="G8" s="24">
+        <v>33.950000000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="19">
+        <v>45872</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="24">
+        <v>33.950000000000003</v>
+      </c>
+      <c r="G9" s="23"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="36">
+        <v>33.950000000000003</v>
+      </c>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="25">
+        <v>33.950000000000003</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13C35AD4-F323-4FD6-9A1E-0B9E74FB09B1}">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="19">
+        <v>45870</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" s="23"/>
+      <c r="G8" s="24">
+        <v>420.07</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="19">
+        <v>45870</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="24">
+        <v>420.07</v>
+      </c>
+      <c r="G9" s="23"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="36">
+        <v>420.07</v>
+      </c>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="25">
+        <v>420.07</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38A9830F-CF73-48B3-B94C-CCED671A37F9}">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="19">
+        <v>45869</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="23"/>
+      <c r="G8" s="24">
+        <v>306.04000000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="19">
+        <v>45869</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="24">
+        <v>306.04000000000002</v>
+      </c>
+      <c r="G9" s="23"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="36">
+        <v>306.04000000000002</v>
+      </c>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="25">
+        <v>306.04000000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1C8857A-9A47-44D1-A1CD-83762CA892B4}">
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="19">
+        <v>45860</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="23"/>
+      <c r="G8" s="24">
+        <v>111.59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="19">
+        <v>45862</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="F9" s="24">
+        <v>111.59</v>
+      </c>
+      <c r="G9" s="23"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="19">
+        <v>45863</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="24">
+        <v>100</v>
+      </c>
+      <c r="G10" s="23"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="19">
+        <v>45863</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" s="23"/>
+      <c r="G11" s="24">
+        <v>65.989999999999995</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="19">
+        <v>45867</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" s="24">
+        <v>65.989999999999995</v>
+      </c>
+      <c r="G12" s="23"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="19">
+        <v>45869</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" s="23"/>
+      <c r="G13" s="24">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="19">
+        <v>45870</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="23"/>
+      <c r="G14" s="24">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="19">
+        <v>45870</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" s="23"/>
+      <c r="G15" s="24">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="19">
+        <v>45871</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" s="23"/>
+      <c r="G16" s="24">
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="19">
+        <v>45871</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" s="24">
+        <v>50.4</v>
+      </c>
+      <c r="G17" s="23"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="19">
+        <v>45878</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" s="23"/>
+      <c r="G18" s="24">
+        <v>531.14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="19">
+        <v>45878</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="F19" s="24">
+        <v>531.14</v>
+      </c>
+      <c r="G19" s="23"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="19">
+        <v>45881</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" s="23"/>
+      <c r="G20" s="24">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="19">
+        <v>45881</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="F21" s="24">
+        <v>10.8</v>
+      </c>
+      <c r="G21" s="23"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="36">
+        <v>869.92</v>
+      </c>
+      <c r="B22" s="36"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="25">
+        <v>869.92</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
 </file>